--- a/weather_data.xlsx
+++ b/weather_data.xlsx
@@ -413,10 +413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
           <t>city</t>
@@ -490,6 +495,138 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>scattered clouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15.49000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14.92000000000002</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20.376</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-13 18:41:29</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1021</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>15.49000000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14.92000000000002</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20.376</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-13 18:41:35</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>70</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1021</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15.49000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14.92000000000002</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20.376</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-13 18:41:41</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>70</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1021</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>14.71000000000004</v>
+      </c>
+      <c r="E6" t="n">
+        <v>18.504</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-13 18:53:08</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>72</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1021</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
         </is>
       </c>
     </row>
